--- a/03_Outputs/all/03_DS/ds_idx14_seguridad.xlsx
+++ b/03_Outputs/all/03_DS/ds_idx14_seguridad.xlsx
@@ -403,19 +403,19 @@
         </is>
       </c>
       <c r="C2">
-        <v>0.02229562137752913</v>
+        <v>0.02229562137753165</v>
       </c>
       <c r="D2">
-        <v>3.232696814701218</v>
+        <v>3.232696814701217</v>
       </c>
       <c r="E2">
-        <v>-0.4085123896668373</v>
+        <v>-0.4085123896668377</v>
       </c>
       <c r="F2">
-        <v>-1.120868416112343</v>
+        <v>-1.120868416112339</v>
       </c>
       <c r="G2">
-        <v>0.4500999512678999</v>
+        <v>0.4500999512679</v>
       </c>
     </row>
     <row r="3">
@@ -430,19 +430,19 @@
         </is>
       </c>
       <c r="C3">
-        <v>0.4186399771408081</v>
+        <v>0.4186399771408098</v>
       </c>
       <c r="D3">
-        <v>1.182678208554924</v>
+        <v>1.182678208554921</v>
       </c>
       <c r="E3">
-        <v>2.362449534010902</v>
+        <v>2.3624495340109</v>
       </c>
       <c r="F3">
-        <v>-0.38024083319456</v>
+        <v>-0.3802408331945609</v>
       </c>
       <c r="G3">
-        <v>0.3521665641876557</v>
+        <v>0.3521665641876552</v>
       </c>
     </row>
     <row r="4">
@@ -457,19 +457,19 @@
         </is>
       </c>
       <c r="C4">
-        <v>1.796215739671543</v>
+        <v>1.796215739671542</v>
       </c>
       <c r="D4">
         <v>-1.437758938551524</v>
       </c>
       <c r="E4">
-        <v>-0.5980558032967733</v>
+        <v>-0.5980558032967755</v>
       </c>
       <c r="F4">
-        <v>-0.3287222045946594</v>
+        <v>-0.3287222045946587</v>
       </c>
       <c r="G4">
-        <v>0.2066757114866908</v>
+        <v>0.2066757114866901</v>
       </c>
     </row>
     <row r="5">
@@ -484,19 +484,19 @@
         </is>
       </c>
       <c r="C5">
-        <v>1.102210502570652</v>
+        <v>1.102210502570651</v>
       </c>
       <c r="D5">
         <v>-1.086423647102372</v>
       </c>
       <c r="E5">
-        <v>-0.9908995013441143</v>
+        <v>-0.9908995013441163</v>
       </c>
       <c r="F5">
-        <v>-0.3532785417764677</v>
+        <v>-0.3532785417764664</v>
       </c>
       <c r="G5">
-        <v>-0.2654297656509091</v>
+        <v>-0.2654297656509095</v>
       </c>
     </row>
     <row r="6">
@@ -511,19 +511,19 @@
         </is>
       </c>
       <c r="C6">
-        <v>0.5798344052062184</v>
+        <v>0.5798344052062181</v>
       </c>
       <c r="D6">
-        <v>-0.5330553964764023</v>
+        <v>-0.5330553964764029</v>
       </c>
       <c r="E6">
-        <v>0.1084966266919248</v>
+        <v>0.1084966266919231</v>
       </c>
       <c r="F6">
-        <v>-0.3391865564742303</v>
+        <v>-0.33918655647423</v>
       </c>
       <c r="G6">
-        <v>-0.4259815981336715</v>
+        <v>-0.4259815981336719</v>
       </c>
     </row>
     <row r="7">
@@ -538,19 +538,19 @@
         </is>
       </c>
       <c r="C7">
-        <v>-1.461843693306129</v>
+        <v>-1.461843693306128</v>
       </c>
       <c r="D7">
-        <v>-0.2140428633881779</v>
+        <v>-0.2140428633881776</v>
       </c>
       <c r="E7">
-        <v>0.08862110230998384</v>
+        <v>0.08862110230998269</v>
       </c>
       <c r="F7">
-        <v>-0.1949899366163141</v>
+        <v>-0.1949899366163129</v>
       </c>
       <c r="G7">
-        <v>-0.01553336719039323</v>
+        <v>-0.01553336719039279</v>
       </c>
     </row>
     <row r="8">
@@ -568,16 +568,16 @@
         <v>-0.6989224479090401</v>
       </c>
       <c r="D8">
-        <v>0.5326299370881559</v>
+        <v>0.5326299370881558</v>
       </c>
       <c r="E8">
-        <v>-1.224634885952741</v>
+        <v>-1.224634885952742</v>
       </c>
       <c r="F8">
-        <v>-0.5617440604155781</v>
+        <v>-0.5617440604155757</v>
       </c>
       <c r="G8">
-        <v>-1.095490471750342</v>
+        <v>-1.095490471750341</v>
       </c>
     </row>
     <row r="9">
@@ -592,19 +592,19 @@
         </is>
       </c>
       <c r="C9">
-        <v>0.4360924973998349</v>
+        <v>0.4360924973998344</v>
       </c>
       <c r="D9">
-        <v>-0.5982114733045071</v>
+        <v>-0.5982114733045083</v>
       </c>
       <c r="E9">
-        <v>0.8903990926889915</v>
+        <v>0.8903990926889903</v>
       </c>
       <c r="F9">
-        <v>0.06193125380379284</v>
+        <v>0.06193125380379222</v>
       </c>
       <c r="G9">
-        <v>-0.9199175350395551</v>
+        <v>-0.9199175350395553</v>
       </c>
     </row>
     <row r="10">
@@ -619,16 +619,16 @@
         </is>
       </c>
       <c r="C10">
-        <v>-0.9442829831271111</v>
+        <v>-0.9442829831271119</v>
       </c>
       <c r="D10">
         <v>-1.323464110986006</v>
       </c>
       <c r="E10">
-        <v>-0.4835471076074533</v>
+        <v>-0.4835471076074547</v>
       </c>
       <c r="F10">
-        <v>0.318964120201852</v>
+        <v>0.3189641202018529</v>
       </c>
       <c r="G10">
         <v>-0.1974076961736443</v>
@@ -646,19 +646,19 @@
         </is>
       </c>
       <c r="C11">
-        <v>-5.396037575192892</v>
+        <v>-5.39603757519289</v>
       </c>
       <c r="D11">
-        <v>-0.09531437659013585</v>
+        <v>-0.09531437659013273</v>
       </c>
       <c r="E11">
-        <v>0.1873851091696668</v>
+        <v>0.1873851091696654</v>
       </c>
       <c r="F11">
-        <v>-0.6774706721975436</v>
+        <v>-0.6774706721975415</v>
       </c>
       <c r="G11">
-        <v>-0.03017150882241969</v>
+        <v>-0.03017150882241717</v>
       </c>
     </row>
     <row r="12">
@@ -673,19 +673,19 @@
         </is>
       </c>
       <c r="C12">
-        <v>0.06506089704054344</v>
+        <v>0.06506089704054337</v>
       </c>
       <c r="D12">
-        <v>-0.5241235510614298</v>
+        <v>-0.5241235510614305</v>
       </c>
       <c r="E12">
-        <v>0.1826128689504089</v>
+        <v>0.1826128689504076</v>
       </c>
       <c r="F12">
-        <v>-0.0382788932106482</v>
+        <v>-0.03827889321064776</v>
       </c>
       <c r="G12">
-        <v>-0.165638849201751</v>
+        <v>-0.1656388492017512</v>
       </c>
     </row>
     <row r="13">
@@ -703,16 +703,16 @@
         <v>0.2669332828002303</v>
       </c>
       <c r="D13">
-        <v>-0.1963570817600916</v>
+        <v>-0.1963570817600924</v>
       </c>
       <c r="E13">
-        <v>0.3033903893233481</v>
+        <v>0.3033903893233467</v>
       </c>
       <c r="F13">
-        <v>-0.2957870511841555</v>
+        <v>-0.2957870511841551</v>
       </c>
       <c r="G13">
-        <v>-0.433585912088679</v>
+        <v>-0.4335859120886792</v>
       </c>
     </row>
     <row r="14">
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="C14">
-        <v>-0.7222180714605767</v>
+        <v>-0.7222180714605749</v>
       </c>
       <c r="D14">
         <v>1.756695196667019</v>
       </c>
       <c r="E14">
-        <v>0.04737425877157507</v>
+        <v>0.04737425877157386</v>
       </c>
       <c r="F14">
-        <v>-0.9796020780711149</v>
+        <v>-0.9796020780711124</v>
       </c>
       <c r="G14">
-        <v>0.5709456679467309</v>
+        <v>0.5709456679467313</v>
       </c>
     </row>
     <row r="15">
@@ -760,13 +760,13 @@
         <v>-1.324397597241762</v>
       </c>
       <c r="E15">
-        <v>-0.7357222999327405</v>
+        <v>-0.7357222999327426</v>
       </c>
       <c r="F15">
-        <v>-0.2632772502068692</v>
+        <v>-0.2632772502068684</v>
       </c>
       <c r="G15">
-        <v>0.3268136553331369</v>
+        <v>0.3268136553331363</v>
       </c>
     </row>
     <row r="16">
@@ -781,19 +781,19 @@
         </is>
       </c>
       <c r="C16">
-        <v>-1.731377005363331</v>
+        <v>-1.73137700536333</v>
       </c>
       <c r="D16">
-        <v>0.2352844212710982</v>
+        <v>0.2352844212710967</v>
       </c>
       <c r="E16">
         <v>2.292048877405514</v>
       </c>
       <c r="F16">
-        <v>0.7461616264537496</v>
+        <v>0.7461616264537487</v>
       </c>
       <c r="G16">
-        <v>0.8577448943219088</v>
+        <v>0.8577448943219087</v>
       </c>
     </row>
     <row r="17">
@@ -808,19 +808,19 @@
         </is>
       </c>
       <c r="C17">
-        <v>1.244614965819016</v>
+        <v>1.244614965819018</v>
       </c>
       <c r="D17">
-        <v>3.305428319643103</v>
+        <v>3.305428319643098</v>
       </c>
       <c r="E17">
-        <v>-2.730095033297271</v>
+        <v>-2.730095033297267</v>
       </c>
       <c r="F17">
-        <v>2.373619824368522</v>
+        <v>2.373619824368527</v>
       </c>
       <c r="G17">
-        <v>0.2491465397734221</v>
+        <v>0.2491465397734204</v>
       </c>
     </row>
     <row r="18">
@@ -835,19 +835,19 @@
         </is>
       </c>
       <c r="C18">
-        <v>0.3548165611504974</v>
+        <v>0.354816561150498</v>
       </c>
       <c r="D18">
-        <v>0.385364109399462</v>
+        <v>0.3853641093994614</v>
       </c>
       <c r="E18">
-        <v>0.01988992260059723</v>
+        <v>0.01988992260059547</v>
       </c>
       <c r="F18">
-        <v>-0.8156478011467593</v>
+        <v>-0.8156478011467581</v>
       </c>
       <c r="G18">
-        <v>0.06865398418409727</v>
+        <v>0.06865398418409721</v>
       </c>
     </row>
     <row r="19">
@@ -862,19 +862,19 @@
         </is>
       </c>
       <c r="C19">
-        <v>0.5876836178134767</v>
+        <v>0.5876836178134758</v>
       </c>
       <c r="D19">
-        <v>-1.316756545872894</v>
+        <v>-1.316756545872896</v>
       </c>
       <c r="E19">
-        <v>0.2346325823181745</v>
+        <v>0.2346325823181732</v>
       </c>
       <c r="F19">
-        <v>0.390542129250592</v>
+        <v>0.3905421292505917</v>
       </c>
       <c r="G19">
-        <v>-0.6521628633828609</v>
+        <v>-0.6521628633828617</v>
       </c>
     </row>
     <row r="20">
@@ -889,19 +889,19 @@
         </is>
       </c>
       <c r="C20">
-        <v>0.6908054521773107</v>
+        <v>0.6908054521773117</v>
       </c>
       <c r="D20">
-        <v>1.312834759502753</v>
+        <v>1.312834759502752</v>
       </c>
       <c r="E20">
-        <v>-1.142174737691964</v>
+        <v>-1.142174737691965</v>
       </c>
       <c r="F20">
-        <v>-0.8682573574584544</v>
+        <v>-0.8682573574584515</v>
       </c>
       <c r="G20">
-        <v>0.06086766321081848</v>
+        <v>0.06086766321081837</v>
       </c>
     </row>
     <row r="21">
@@ -916,16 +916,16 @@
         </is>
       </c>
       <c r="C21">
-        <v>-0.6371613467813434</v>
+        <v>-0.6371613467813435</v>
       </c>
       <c r="D21">
-        <v>-0.08876022950153628</v>
+        <v>-0.08876022950153757</v>
       </c>
       <c r="E21">
         <v>0.3234211339360554</v>
       </c>
       <c r="F21">
-        <v>0.6170175715894508</v>
+        <v>0.6170175715894514</v>
       </c>
       <c r="G21">
         <v>-1.066589013163539</v>
@@ -943,19 +943,19 @@
         </is>
       </c>
       <c r="C22">
-        <v>-0.2679784860497952</v>
+        <v>-0.2679784860497949</v>
       </c>
       <c r="D22">
-        <v>0.2616339649959222</v>
+        <v>0.2616339649959218</v>
       </c>
       <c r="E22">
-        <v>0.4337907340299159</v>
+        <v>0.4337907340299142</v>
       </c>
       <c r="F22">
-        <v>-0.6932649785455418</v>
+        <v>-0.6932649785455411</v>
       </c>
       <c r="G22">
-        <v>-0.4982429264163824</v>
+        <v>-0.4982429264163822</v>
       </c>
     </row>
     <row r="23">
@@ -970,16 +970,16 @@
         </is>
       </c>
       <c r="C23">
-        <v>-0.6517984195906865</v>
+        <v>-0.6517984195906863</v>
       </c>
       <c r="D23">
-        <v>0.6721776317030363</v>
+        <v>0.672177631703034</v>
       </c>
       <c r="E23">
-        <v>-0.2678077191839165</v>
+        <v>-0.267807719183915</v>
       </c>
       <c r="F23">
-        <v>1.330986741292167</v>
+        <v>1.330986741292169</v>
       </c>
       <c r="G23">
         <v>-1.240065360076277</v>
@@ -997,19 +997,19 @@
         </is>
       </c>
       <c r="C24">
-        <v>-3.809626130016462</v>
+        <v>-3.809626130016461</v>
       </c>
       <c r="D24">
-        <v>0.8662630729666503</v>
+        <v>0.8662630729666518</v>
       </c>
       <c r="E24">
-        <v>-0.6070012236102147</v>
+        <v>-0.6070012236102149</v>
       </c>
       <c r="F24">
-        <v>-0.1146391842263051</v>
+        <v>-0.1146391842263016</v>
       </c>
       <c r="G24">
-        <v>0.9458288766024153</v>
+        <v>0.9458288766024169</v>
       </c>
     </row>
     <row r="25">
@@ -1024,19 +1024,19 @@
         </is>
       </c>
       <c r="C25">
-        <v>0.2103324541422266</v>
+        <v>0.2103324541422258</v>
       </c>
       <c r="D25">
-        <v>-1.217345998633751</v>
+        <v>-1.217345998633752</v>
       </c>
       <c r="E25">
-        <v>0.5101631599810627</v>
+        <v>0.5101631599810618</v>
       </c>
       <c r="F25">
-        <v>0.5332484583186734</v>
+        <v>0.5332484583186727</v>
       </c>
       <c r="G25">
-        <v>-0.7370899239159375</v>
+        <v>-0.737089923915938</v>
       </c>
     </row>
     <row r="26">
@@ -1051,19 +1051,19 @@
         </is>
       </c>
       <c r="C26">
-        <v>-2.991412710327727</v>
+        <v>-2.991412710327726</v>
       </c>
       <c r="D26">
-        <v>-0.8874286776493504</v>
+        <v>-0.8874286776493487</v>
       </c>
       <c r="E26">
-        <v>-0.2750197852850899</v>
+        <v>-0.2750197852850907</v>
       </c>
       <c r="F26">
-        <v>0.2247395313525795</v>
+        <v>0.2247395313525816</v>
       </c>
       <c r="G26">
-        <v>1.141157254675457</v>
+        <v>1.141157254675458</v>
       </c>
     </row>
     <row r="27">
@@ -1081,16 +1081,16 @@
         <v>1.283679536979136</v>
       </c>
       <c r="D27">
-        <v>0.3901191428211204</v>
+        <v>0.3901191428211178</v>
       </c>
       <c r="E27">
-        <v>-1.491943583651731</v>
+        <v>-1.49194358365173</v>
       </c>
       <c r="F27">
-        <v>1.50215751670881</v>
+        <v>1.502157516708812</v>
       </c>
       <c r="G27">
-        <v>0.03314119926094269</v>
+        <v>0.03314119926094131</v>
       </c>
     </row>
     <row r="28">
@@ -1105,19 +1105,19 @@
         </is>
       </c>
       <c r="C28">
-        <v>0.5963599651702872</v>
+        <v>0.5963599651702879</v>
       </c>
       <c r="D28">
-        <v>0.466910680026352</v>
+        <v>0.4669106800263516</v>
       </c>
       <c r="E28">
-        <v>0.4143061052246165</v>
+        <v>0.4143061052246142</v>
       </c>
       <c r="F28">
-        <v>-1.196356995983628</v>
+        <v>-1.196356995983627</v>
       </c>
       <c r="G28">
-        <v>-0.1177046804501157</v>
+        <v>-0.1177046804501156</v>
       </c>
     </row>
     <row r="29">
@@ -1132,19 +1132,19 @@
         </is>
       </c>
       <c r="C29">
-        <v>-1.546733344965083</v>
+        <v>-1.546733344965082</v>
       </c>
       <c r="D29">
-        <v>0.1538804518206553</v>
+        <v>0.1538804518206544</v>
       </c>
       <c r="E29">
-        <v>-0.08431670795050449</v>
+        <v>-0.0843167079505036</v>
       </c>
       <c r="F29">
-        <v>1.106180614445849</v>
+        <v>1.106180614445851</v>
       </c>
       <c r="G29">
-        <v>0.5007283442346504</v>
+        <v>0.5007283442346501</v>
       </c>
     </row>
     <row r="30">
@@ -1159,19 +1159,19 @@
         </is>
       </c>
       <c r="C30">
-        <v>0.4566481834818631</v>
+        <v>0.4566481834818623</v>
       </c>
       <c r="D30">
-        <v>-1.429336765397877</v>
+        <v>-1.429336765397878</v>
       </c>
       <c r="E30">
-        <v>-0.4009544687544305</v>
+        <v>-0.4009544687544315</v>
       </c>
       <c r="F30">
-        <v>0.4711370364646067</v>
+        <v>0.4711370364646071</v>
       </c>
       <c r="G30">
-        <v>-0.3027106594859388</v>
+        <v>-0.3027106594859394</v>
       </c>
     </row>
     <row r="31">
@@ -1189,16 +1189,16 @@
         <v>1.31912694817264</v>
       </c>
       <c r="D31">
-        <v>-0.5069667679040369</v>
+        <v>-0.5069667679040383</v>
       </c>
       <c r="E31">
-        <v>-0.7838393739395781</v>
+        <v>-0.7838393739395789</v>
       </c>
       <c r="F31">
-        <v>0.270564277234588</v>
+        <v>0.2705642772345894</v>
       </c>
       <c r="G31">
-        <v>-0.1176610005361809</v>
+        <v>-0.1176610005361818</v>
       </c>
     </row>
     <row r="32">
@@ -1213,19 +1213,19 @@
         </is>
       </c>
       <c r="C32">
-        <v>1.721691353135194</v>
+        <v>1.721691353135193</v>
       </c>
       <c r="D32">
-        <v>-0.5615554331001786</v>
+        <v>-0.5615554331001804</v>
       </c>
       <c r="E32">
-        <v>-0.5376438643003797</v>
+        <v>-0.5376438643003804</v>
       </c>
       <c r="F32">
-        <v>0.3950250032542371</v>
+        <v>0.3950250032542378</v>
       </c>
       <c r="G32">
-        <v>-0.3122372026905558</v>
+        <v>-0.3122372026905569</v>
       </c>
     </row>
     <row r="33">
@@ -1240,19 +1240,19 @@
         </is>
       </c>
       <c r="C33">
-        <v>0.5166241446541444</v>
+        <v>0.5166241446541457</v>
       </c>
       <c r="D33">
-        <v>0.6794323862405828</v>
+        <v>0.6794323862405808</v>
       </c>
       <c r="E33">
-        <v>0.6566473821339647</v>
+        <v>0.6566473821339645</v>
       </c>
       <c r="F33">
-        <v>0.3682059556744123</v>
+        <v>0.3682059556744131</v>
       </c>
       <c r="G33">
-        <v>0.868542875473635</v>
+        <v>0.8685428754736342</v>
       </c>
     </row>
     <row r="34">
@@ -1267,19 +1267,19 @@
         </is>
       </c>
       <c r="C34">
-        <v>0.2995026775530477</v>
+        <v>0.2995026775530492</v>
       </c>
       <c r="D34">
-        <v>2.194250912593332</v>
+        <v>2.19425091259333</v>
       </c>
       <c r="E34">
         <v>-0.6543451021786834</v>
       </c>
       <c r="F34">
-        <v>-0.3085160768362907</v>
+        <v>-0.3085160768362877</v>
       </c>
       <c r="G34">
-        <v>-0.1094231623074826</v>
+        <v>-0.1094231623074829</v>
       </c>
     </row>
     <row r="35">
@@ -1294,19 +1294,19 @@
         </is>
       </c>
       <c r="C35">
-        <v>2.080641659121905</v>
+        <v>2.080641659121908</v>
       </c>
       <c r="D35">
-        <v>3.339550927983309</v>
+        <v>3.339550927983303</v>
       </c>
       <c r="E35">
-        <v>-0.1194579527961233</v>
+        <v>-0.1194579527961197</v>
       </c>
       <c r="F35">
-        <v>2.110063985489419</v>
+        <v>2.110063985489422</v>
       </c>
       <c r="G35">
-        <v>0.7063380757305153</v>
+        <v>0.7063380757305133</v>
       </c>
     </row>
     <row r="36">
@@ -1321,19 +1321,19 @@
         </is>
       </c>
       <c r="C36">
-        <v>-1.969056278037959</v>
+        <v>-1.969056278037958</v>
       </c>
       <c r="D36">
-        <v>0.4221431928976538</v>
+        <v>0.4221431928976553</v>
       </c>
       <c r="E36">
-        <v>-1.001111929022786</v>
+        <v>-1.001111929022787</v>
       </c>
       <c r="F36">
-        <v>-1.08310880129209</v>
+        <v>-1.083108801292088</v>
       </c>
       <c r="G36">
-        <v>0.08108771777601105</v>
+        <v>0.08108771777601204</v>
       </c>
     </row>
     <row r="37">
@@ -1348,19 +1348,19 @@
         </is>
       </c>
       <c r="C37">
-        <v>-0.4664697482957684</v>
+        <v>-0.4664697482957677</v>
       </c>
       <c r="D37">
-        <v>0.09040709549541939</v>
+        <v>0.09040709549541948</v>
       </c>
       <c r="E37">
-        <v>0.251404271479919</v>
+        <v>0.2514042714799171</v>
       </c>
       <c r="F37">
-        <v>-0.7251668617210253</v>
+        <v>-0.7251668617210242</v>
       </c>
       <c r="G37">
-        <v>0.4602365576087087</v>
+        <v>0.460236557608709</v>
       </c>
     </row>
     <row r="38">
@@ -1375,19 +1375,19 @@
         </is>
       </c>
       <c r="C38">
-        <v>0.2170057095222901</v>
+        <v>0.2170057095222896</v>
       </c>
       <c r="D38">
-        <v>-0.5309273118285004</v>
+        <v>-0.5309273118285011</v>
       </c>
       <c r="E38">
-        <v>-0.6532207375259002</v>
+        <v>-0.6532207375259012</v>
       </c>
       <c r="F38">
-        <v>0.1116581674398554</v>
+        <v>0.1116581674398566</v>
       </c>
       <c r="G38">
-        <v>-0.713947464236554</v>
+        <v>-0.7139474642365543</v>
       </c>
     </row>
     <row r="39">
@@ -1402,19 +1402,19 @@
         </is>
       </c>
       <c r="C39">
-        <v>0.4258126199832479</v>
+        <v>0.425812619983248</v>
       </c>
       <c r="D39">
-        <v>-0.1692892984397682</v>
+        <v>-0.1692892984397695</v>
       </c>
       <c r="E39">
         <v>-1.367652751314326</v>
       </c>
       <c r="F39">
-        <v>1.045522934431447</v>
+        <v>1.045522934431449</v>
       </c>
       <c r="G39">
-        <v>0.1958909201688388</v>
+        <v>0.195890920168838</v>
       </c>
     </row>
     <row r="40">
@@ -1432,16 +1432,16 @@
         <v>1.285904110637992</v>
       </c>
       <c r="D40">
-        <v>-0.4520643793462517</v>
+        <v>-0.4520643793462538</v>
       </c>
       <c r="E40">
-        <v>0.9887073952619152</v>
+        <v>0.9887073952619143</v>
       </c>
       <c r="F40">
-        <v>0.3357222681513942</v>
+        <v>0.3357222681513937</v>
       </c>
       <c r="G40">
-        <v>0.2781900784144171</v>
+        <v>0.2781900784144161</v>
       </c>
     </row>
     <row r="41">
@@ -1456,19 +1456,19 @@
         </is>
       </c>
       <c r="C41">
-        <v>0.05885201351638499</v>
+        <v>0.05885201351638464</v>
       </c>
       <c r="D41">
-        <v>-0.5148585284047587</v>
+        <v>-0.5148585284047595</v>
       </c>
       <c r="E41">
-        <v>0.4519868960572264</v>
+        <v>0.4519868960572252</v>
       </c>
       <c r="F41">
-        <v>0.06598610421261436</v>
+        <v>0.06598610421261435</v>
       </c>
       <c r="G41">
-        <v>-0.7470249345853428</v>
+        <v>-0.7470249345853431</v>
       </c>
     </row>
     <row r="42">
@@ -1483,19 +1483,19 @@
         </is>
       </c>
       <c r="C42">
-        <v>0.6775980924475156</v>
+        <v>0.6775980924475166</v>
       </c>
       <c r="D42">
-        <v>1.003867753935288</v>
+        <v>1.003867753935287</v>
       </c>
       <c r="E42">
-        <v>0.1173529195110733</v>
+        <v>0.117352919511072</v>
       </c>
       <c r="F42">
-        <v>-0.737870399367994</v>
+        <v>-0.7378703993679928</v>
       </c>
       <c r="G42">
-        <v>-0.06827248395569833</v>
+        <v>-0.06827248395569858</v>
       </c>
     </row>
     <row r="43">
@@ -1510,13 +1510,13 @@
         </is>
       </c>
       <c r="C43">
-        <v>-0.8757940884888705</v>
+        <v>-0.8757940884888697</v>
       </c>
       <c r="D43">
-        <v>-0.703026524475545</v>
+        <v>-0.7030265244755454</v>
       </c>
       <c r="E43">
-        <v>1.061800299459079</v>
+        <v>1.061800299459078</v>
       </c>
       <c r="F43">
         <v>0.3498069627493379</v>
@@ -1537,19 +1537,19 @@
         </is>
       </c>
       <c r="C44">
-        <v>1.053857549547037</v>
+        <v>1.053857549547038</v>
       </c>
       <c r="D44">
-        <v>1.651260583781898</v>
+        <v>1.651260583781896</v>
       </c>
       <c r="E44">
         <v>0.5463312116812152</v>
       </c>
       <c r="F44">
-        <v>-0.03165817932723782</v>
+        <v>-0.03165817932723659</v>
       </c>
       <c r="G44">
-        <v>0.3416018551796853</v>
+        <v>0.3416018551796846</v>
       </c>
     </row>
     <row r="45">
@@ -1564,19 +1564,19 @@
         </is>
       </c>
       <c r="C45">
-        <v>1.142736092829915</v>
+        <v>1.142736092829914</v>
       </c>
       <c r="D45">
         <v>-1.737225339490251</v>
       </c>
       <c r="E45">
-        <v>-0.7283480612188118</v>
+        <v>-0.7283480612188138</v>
       </c>
       <c r="F45">
-        <v>0.09708787431764836</v>
+        <v>0.09708787431764888</v>
       </c>
       <c r="G45">
-        <v>-0.1754066668331652</v>
+        <v>-0.1754066668331659</v>
       </c>
     </row>
     <row r="46">
@@ -1594,16 +1594,16 @@
         <v>-1.757417979637796</v>
       </c>
       <c r="D46">
-        <v>0.1019171470605502</v>
+        <v>0.101917147060552</v>
       </c>
       <c r="E46">
-        <v>-1.279449379143826</v>
+        <v>-1.279449379143827</v>
       </c>
       <c r="F46">
-        <v>-0.8236742675833637</v>
+        <v>-0.8236742675833607</v>
       </c>
       <c r="G46">
-        <v>0.3690303122730939</v>
+        <v>0.3690303122730947</v>
       </c>
     </row>
     <row r="47">
@@ -1621,16 +1621,16 @@
         <v>1.265768474261773</v>
       </c>
       <c r="D47">
-        <v>0.4169195914534677</v>
+        <v>0.4169195914534659</v>
       </c>
       <c r="E47">
         <v>-1.480626504567251</v>
       </c>
       <c r="F47">
-        <v>0.4763514693158376</v>
+        <v>0.4763514693158402</v>
       </c>
       <c r="G47">
-        <v>-0.2053759456103813</v>
+        <v>-0.2053759456103822</v>
       </c>
     </row>
     <row r="48">
@@ -1648,16 +1648,16 @@
         <v>1.490551643440026</v>
       </c>
       <c r="D48">
-        <v>-0.1179809066773686</v>
+        <v>-0.1179809066773697</v>
       </c>
       <c r="E48">
-        <v>-0.7613728098380869</v>
+        <v>-0.7613728098380885</v>
       </c>
       <c r="F48">
-        <v>-0.4661046296685551</v>
+        <v>-0.4661046296685537</v>
       </c>
       <c r="G48">
-        <v>0.05860094422200474</v>
+        <v>0.05860094422200399</v>
       </c>
     </row>
     <row r="49">
@@ -1672,19 +1672,19 @@
         </is>
       </c>
       <c r="C49">
-        <v>0.6871918563249392</v>
+        <v>0.6871918563249388</v>
       </c>
       <c r="D49">
-        <v>-0.6765854006630901</v>
+        <v>-0.6765854006630907</v>
       </c>
       <c r="E49">
-        <v>-0.3128285284519689</v>
+        <v>-0.3128285284519706</v>
       </c>
       <c r="F49">
-        <v>-0.3245838919526098</v>
+        <v>-0.3245838919526091</v>
       </c>
       <c r="G49">
-        <v>-0.4125469091154657</v>
+        <v>-0.412546909115466</v>
       </c>
     </row>
     <row r="50">
@@ -1699,19 +1699,19 @@
         </is>
       </c>
       <c r="C50">
-        <v>0.5310459575086269</v>
+        <v>0.531045957508627</v>
       </c>
       <c r="D50">
-        <v>-0.7665634040192979</v>
+        <v>-0.7665634040192996</v>
       </c>
       <c r="E50">
-        <v>0.4314573534577091</v>
+        <v>0.4314573534577087</v>
       </c>
       <c r="F50">
-        <v>0.7810505461833974</v>
+        <v>0.7810505461833975</v>
       </c>
       <c r="G50">
-        <v>0.4548437450286336</v>
+        <v>0.4548437450286327</v>
       </c>
     </row>
     <row r="51">
@@ -1726,19 +1726,19 @@
         </is>
       </c>
       <c r="C51">
-        <v>0.4540376355304661</v>
+        <v>0.4540376355304672</v>
       </c>
       <c r="D51">
-        <v>1.392236461757672</v>
+        <v>1.392236461757669</v>
       </c>
       <c r="E51">
-        <v>-0.05153469169418691</v>
+        <v>-0.05153469169418479</v>
       </c>
       <c r="F51">
-        <v>1.563342832524025</v>
+        <v>1.563342832524027</v>
       </c>
       <c r="G51">
-        <v>-0.1520092919458251</v>
+        <v>-0.1520092919458262</v>
       </c>
     </row>
     <row r="52">
@@ -1753,16 +1753,16 @@
         </is>
       </c>
       <c r="C52">
-        <v>0.6247343353702213</v>
+        <v>0.6247343353702212</v>
       </c>
       <c r="D52">
-        <v>-0.3791935329288272</v>
+        <v>-0.3791935329288269</v>
       </c>
       <c r="E52">
-        <v>-0.5714456618710924</v>
+        <v>-0.5714456618710952</v>
       </c>
       <c r="F52">
-        <v>-1.231082816047584</v>
+        <v>-1.231082816047583</v>
       </c>
       <c r="G52">
         <v>-0.3032028750958755</v>
@@ -1780,19 +1780,19 @@
         </is>
       </c>
       <c r="C53">
-        <v>0.7867082253039001</v>
+        <v>0.7867082253039004</v>
       </c>
       <c r="D53">
-        <v>0.02633463550214403</v>
+        <v>0.02633463550214282</v>
       </c>
       <c r="E53">
-        <v>1.03650807752893</v>
+        <v>1.036508077528928</v>
       </c>
       <c r="F53">
-        <v>-0.5313687570348826</v>
+        <v>-0.5313687570348831</v>
       </c>
       <c r="G53">
-        <v>-0.3415870880350245</v>
+        <v>-0.3415870880350247</v>
       </c>
     </row>
     <row r="54">
@@ -1807,19 +1807,19 @@
         </is>
       </c>
       <c r="C54">
-        <v>0.04580489951103904</v>
+        <v>0.04580489951103926</v>
       </c>
       <c r="D54">
-        <v>-0.9624924214934585</v>
+        <v>-0.9624924214934596</v>
       </c>
       <c r="E54">
-        <v>-0.2431099098585792</v>
+        <v>-0.2431099098585793</v>
       </c>
       <c r="F54">
-        <v>0.9646453264077834</v>
+        <v>0.9646453264077846</v>
       </c>
       <c r="G54">
-        <v>0.9168542828359308</v>
+        <v>0.9168542828359302</v>
       </c>
     </row>
     <row r="55">
@@ -1834,19 +1834,19 @@
         </is>
       </c>
       <c r="C55">
-        <v>0.6027425497461288</v>
+        <v>0.6027425497461283</v>
       </c>
       <c r="D55">
         <v>-1.15098277933565</v>
       </c>
       <c r="E55">
-        <v>-0.8500940541319472</v>
+        <v>-0.8500940541319493</v>
       </c>
       <c r="F55">
-        <v>-0.2963510436379377</v>
+        <v>-0.2963510436379365</v>
       </c>
       <c r="G55">
-        <v>0.1102235582253507</v>
+        <v>0.1102235582253503</v>
       </c>
     </row>
     <row r="56">
@@ -1861,19 +1861,19 @@
         </is>
       </c>
       <c r="C56">
-        <v>0.7263516201037116</v>
+        <v>0.7263516201037127</v>
       </c>
       <c r="D56">
-        <v>1.909406858648244</v>
+        <v>1.909406858648242</v>
       </c>
       <c r="E56">
-        <v>-1.105819509864158</v>
+        <v>-1.105819509864157</v>
       </c>
       <c r="F56">
-        <v>0.214125283855183</v>
+        <v>0.2141252838551861</v>
       </c>
       <c r="G56">
-        <v>-0.1022727716210237</v>
+        <v>-0.1022727716210243</v>
       </c>
     </row>
     <row r="57">
@@ -1888,19 +1888,19 @@
         </is>
       </c>
       <c r="C57">
-        <v>1.736469112029504</v>
+        <v>1.736469112029506</v>
       </c>
       <c r="D57">
-        <v>0.865828644626381</v>
+        <v>0.8658286446263774</v>
       </c>
       <c r="E57">
         <v>2.530878336364741</v>
       </c>
       <c r="F57">
-        <v>0.2785756528273998</v>
+        <v>0.2785756528273982</v>
       </c>
       <c r="G57">
-        <v>0.9511989915337176</v>
+        <v>0.9511989915337162</v>
       </c>
     </row>
     <row r="58">
@@ -1915,19 +1915,19 @@
         </is>
       </c>
       <c r="C58">
-        <v>0.3439507770216488</v>
+        <v>0.343950777021649</v>
       </c>
       <c r="D58">
-        <v>-0.20517477520089</v>
+        <v>-0.2051747752008908</v>
       </c>
       <c r="E58">
-        <v>0.9514528548127658</v>
+        <v>0.9514528548127639</v>
       </c>
       <c r="F58">
-        <v>-0.6154193982550846</v>
+        <v>-0.6154193982550848</v>
       </c>
       <c r="G58">
-        <v>-0.09236585511892921</v>
+        <v>-0.09236585511892936</v>
       </c>
     </row>
     <row r="59">
@@ -1945,16 +1945,16 @@
         <v>0.3130222445415451</v>
       </c>
       <c r="D59">
-        <v>0.1646880224463395</v>
+        <v>0.1646880224463368</v>
       </c>
       <c r="E59">
-        <v>1.306123723744439</v>
+        <v>1.30612372374444</v>
       </c>
       <c r="F59">
-        <v>0.9293559371898363</v>
+        <v>0.9293559371898356</v>
       </c>
       <c r="G59">
-        <v>-1.165519719943914</v>
+        <v>-1.165519719943915</v>
       </c>
     </row>
     <row r="60">
@@ -1969,19 +1969,19 @@
         </is>
       </c>
       <c r="C60">
-        <v>1.585461606290308</v>
+        <v>1.585461606290309</v>
       </c>
       <c r="D60">
-        <v>0.6450411098259271</v>
+        <v>0.645041109825925</v>
       </c>
       <c r="E60">
-        <v>0.5942015673126829</v>
+        <v>0.5942015673126818</v>
       </c>
       <c r="F60">
-        <v>-0.3026734206181425</v>
+        <v>-0.302673420618142</v>
       </c>
       <c r="G60">
-        <v>0.3725590948111022</v>
+        <v>0.3725590948111014</v>
       </c>
     </row>
     <row r="61">
@@ -1999,13 +1999,13 @@
         <v>-2.987065070931428</v>
       </c>
       <c r="D61">
-        <v>-1.362556784877454</v>
+        <v>-1.362556784877453</v>
       </c>
       <c r="E61">
-        <v>-0.4701216909016298</v>
+        <v>-0.4701216909016301</v>
       </c>
       <c r="F61">
-        <v>0.8125466917829011</v>
+        <v>0.812546691782903</v>
       </c>
       <c r="G61">
         <v>1.774553853971518</v>
@@ -2023,19 +2023,19 @@
         </is>
       </c>
       <c r="C62">
-        <v>0.1671816553518905</v>
+        <v>0.1671816553518908</v>
       </c>
       <c r="D62">
-        <v>0.4012284985190704</v>
+        <v>0.4012284985190699</v>
       </c>
       <c r="E62">
-        <v>-0.4061049970255876</v>
+        <v>-0.4061049970255891</v>
       </c>
       <c r="F62">
-        <v>-0.6727866692529527</v>
+        <v>-0.6727866692529512</v>
       </c>
       <c r="G62">
-        <v>-0.4790850959816139</v>
+        <v>-0.4790850959816138</v>
       </c>
     </row>
     <row r="63">
@@ -2050,19 +2050,19 @@
         </is>
       </c>
       <c r="C63">
-        <v>1.334279453450948</v>
+        <v>1.334279453450949</v>
       </c>
       <c r="D63">
-        <v>0.3523441625336379</v>
+        <v>0.3523441625336358</v>
       </c>
       <c r="E63">
-        <v>1.397095046336525</v>
+        <v>1.397095046336524</v>
       </c>
       <c r="F63">
-        <v>-0.2406076205403455</v>
+        <v>-0.2406076205403461</v>
       </c>
       <c r="G63">
-        <v>0.1277499607810831</v>
+        <v>0.1277499607810824</v>
       </c>
     </row>
     <row r="64">
@@ -2077,19 +2077,19 @@
         </is>
       </c>
       <c r="C64">
-        <v>0.6462739121797414</v>
+        <v>0.6462739121797433</v>
       </c>
       <c r="D64">
-        <v>1.507910870864846</v>
+        <v>1.507910870864845</v>
       </c>
       <c r="E64">
-        <v>1.028824167633408</v>
+        <v>1.028824167633406</v>
       </c>
       <c r="F64">
         <v>-1.465789278678038</v>
       </c>
       <c r="G64">
-        <v>0.4545797288102054</v>
+        <v>0.4545797288102055</v>
       </c>
     </row>
     <row r="65">
@@ -2107,16 +2107,16 @@
         <v>1.329719820633721</v>
       </c>
       <c r="D65">
-        <v>-0.09177122320973269</v>
+        <v>-0.09177122320973387</v>
       </c>
       <c r="E65">
-        <v>0.04159955735251638</v>
+        <v>0.04159955735251465</v>
       </c>
       <c r="F65">
-        <v>-0.4676510371846557</v>
+        <v>-0.4676510371846551</v>
       </c>
       <c r="G65">
-        <v>0.07771325037466074</v>
+        <v>0.07771325037466009</v>
       </c>
     </row>
     <row r="66">
@@ -2131,19 +2131,19 @@
         </is>
       </c>
       <c r="C66">
-        <v>0.5144427350893652</v>
+        <v>0.5144427350893661</v>
       </c>
       <c r="D66">
-        <v>0.4244544836467853</v>
+        <v>0.4244544836467838</v>
       </c>
       <c r="E66">
-        <v>1.781611007099346</v>
+        <v>1.781611007099345</v>
       </c>
       <c r="F66">
-        <v>-0.6917221578080222</v>
+        <v>-0.691722157808023</v>
       </c>
       <c r="G66">
-        <v>0.2013088617138571</v>
+        <v>0.2013088617138568</v>
       </c>
     </row>
     <row r="67">
@@ -2158,19 +2158,19 @@
         </is>
       </c>
       <c r="C67">
-        <v>0.4812219033022986</v>
+        <v>0.4812219033022993</v>
       </c>
       <c r="D67">
-        <v>0.4784746303194026</v>
+        <v>0.4784746303194014</v>
       </c>
       <c r="E67">
-        <v>0.8686076176389325</v>
+        <v>0.8686076176389308</v>
       </c>
       <c r="F67">
-        <v>-0.5780282554770506</v>
+        <v>-0.5780282554770504</v>
       </c>
       <c r="G67">
-        <v>0.0613683240638716</v>
+        <v>0.0613683240638713</v>
       </c>
     </row>
     <row r="68">
@@ -2191,13 +2191,13 @@
         <v>-1.003959513841982</v>
       </c>
       <c r="E68">
-        <v>-0.474853290644359</v>
+        <v>-0.474853290644361</v>
       </c>
       <c r="F68">
-        <v>-0.3961642081837417</v>
+        <v>-0.396164208183741</v>
       </c>
       <c r="G68">
-        <v>-0.1790336740528796</v>
+        <v>-0.17903367405288</v>
       </c>
     </row>
     <row r="69">
@@ -2212,19 +2212,19 @@
         </is>
       </c>
       <c r="C69">
-        <v>-0.693777884897199</v>
+        <v>-0.6937778848972</v>
       </c>
       <c r="D69">
         <v>-1.691738632341436</v>
       </c>
       <c r="E69">
-        <v>-0.2905369275533097</v>
+        <v>-0.2905369275533107</v>
       </c>
       <c r="F69">
-        <v>0.6595189926977902</v>
+        <v>0.6595189926977907</v>
       </c>
       <c r="G69">
-        <v>-0.5431520301716889</v>
+        <v>-0.5431520301716892</v>
       </c>
     </row>
     <row r="70">
@@ -2239,19 +2239,19 @@
         </is>
       </c>
       <c r="C70">
-        <v>-0.02104537535712385</v>
+        <v>-0.02104537535712205</v>
       </c>
       <c r="D70">
-        <v>2.869653252683749</v>
+        <v>2.869653252683747</v>
       </c>
       <c r="E70">
         <v>-0.9024900200819229</v>
       </c>
       <c r="F70">
-        <v>-0.8957721485313336</v>
+        <v>-0.8957721485313299</v>
       </c>
       <c r="G70">
-        <v>-0.2033188400797163</v>
+        <v>-0.2033188400797162</v>
       </c>
     </row>
     <row r="71">
@@ -2266,19 +2266,19 @@
         </is>
       </c>
       <c r="C71">
-        <v>0.4594872974054587</v>
+        <v>0.4594872974054585</v>
       </c>
       <c r="D71">
-        <v>-0.798166084699801</v>
+        <v>-0.7981660846997998</v>
       </c>
       <c r="E71">
-        <v>-1.144811912209269</v>
+        <v>-1.144811912209272</v>
       </c>
       <c r="F71">
-        <v>-1.41252150904512</v>
+        <v>-1.412521509045118</v>
       </c>
       <c r="G71">
-        <v>0.1454456379287852</v>
+        <v>0.1454456379287856</v>
       </c>
     </row>
     <row r="72">
@@ -2293,19 +2293,19 @@
         </is>
       </c>
       <c r="C72">
-        <v>0.6177504975268084</v>
+        <v>0.6177504975268086</v>
       </c>
       <c r="D72">
-        <v>-0.8626407815122976</v>
+        <v>-0.8626407815122977</v>
       </c>
       <c r="E72">
-        <v>-0.5243350258052395</v>
+        <v>-0.5243350258052415</v>
       </c>
       <c r="F72">
-        <v>-0.3121730899806228</v>
+        <v>-0.3121730899806215</v>
       </c>
       <c r="G72">
-        <v>0.6986316699376075</v>
+        <v>0.6986316699376069</v>
       </c>
     </row>
     <row r="73">
@@ -2320,19 +2320,19 @@
         </is>
       </c>
       <c r="C73">
-        <v>-0.8750754523648521</v>
+        <v>-0.8750754523648525</v>
       </c>
       <c r="D73">
         <v>-1.427805537949086</v>
       </c>
       <c r="E73">
-        <v>-0.06824663866420223</v>
+        <v>-0.06824663866420333</v>
       </c>
       <c r="F73">
-        <v>0.4680511738888971</v>
+        <v>0.4680511738888978</v>
       </c>
       <c r="G73">
-        <v>0.2111120879392077</v>
+        <v>0.2111120879392076</v>
       </c>
     </row>
     <row r="74">
@@ -2347,19 +2347,19 @@
         </is>
       </c>
       <c r="C74">
-        <v>0.09907375522513055</v>
+        <v>0.09907375522513068</v>
       </c>
       <c r="D74">
-        <v>-0.682654451792492</v>
+        <v>-0.6826544517924928</v>
       </c>
       <c r="E74">
-        <v>0.5329887070234623</v>
+        <v>0.5329887070234611</v>
       </c>
       <c r="F74">
-        <v>0.06441615470734263</v>
+        <v>0.06441615470734274</v>
       </c>
       <c r="G74">
-        <v>0.3116022086569721</v>
+        <v>0.3116022086569717</v>
       </c>
     </row>
     <row r="75">
@@ -2374,19 +2374,19 @@
         </is>
       </c>
       <c r="C75">
-        <v>0.5295947450620697</v>
+        <v>0.5295947450620696</v>
       </c>
       <c r="D75">
-        <v>-0.7131204895946901</v>
+        <v>-0.7131204895946898</v>
       </c>
       <c r="E75">
-        <v>-0.5198075688711693</v>
+        <v>-0.5198075688711716</v>
       </c>
       <c r="F75">
-        <v>-0.7483736170947325</v>
+        <v>-0.7483736170947312</v>
       </c>
       <c r="G75">
-        <v>0.3205813722190609</v>
+        <v>0.3205813722190608</v>
       </c>
     </row>
     <row r="76">
@@ -2401,16 +2401,16 @@
         </is>
       </c>
       <c r="C76">
-        <v>0.204482298086108</v>
+        <v>0.2044822980861082</v>
       </c>
       <c r="D76">
         <v>-1.044789537648573</v>
       </c>
       <c r="E76">
-        <v>-0.2066562800444743</v>
+        <v>-0.2066562800444765</v>
       </c>
       <c r="F76">
-        <v>-0.3795763045196733</v>
+        <v>-0.3795763045196724</v>
       </c>
       <c r="G76">
         <v>1.029256423159631</v>
@@ -2428,19 +2428,19 @@
         </is>
       </c>
       <c r="C77">
-        <v>0.4956607879068622</v>
+        <v>0.4956607879068623</v>
       </c>
       <c r="D77">
-        <v>-0.8804915441253962</v>
+        <v>-0.8804915441253973</v>
       </c>
       <c r="E77">
-        <v>0.6639931112913408</v>
+        <v>0.6639931112913396</v>
       </c>
       <c r="F77">
-        <v>0.3263295763898414</v>
+        <v>0.3263295763898412</v>
       </c>
       <c r="G77">
-        <v>0.2880340327103317</v>
+        <v>0.2880340327103311</v>
       </c>
     </row>
     <row r="78">
@@ -2455,19 +2455,19 @@
         </is>
       </c>
       <c r="C78">
-        <v>0.8366811555645234</v>
+        <v>0.8366811555645242</v>
       </c>
       <c r="D78">
-        <v>0.8868913043748664</v>
+        <v>0.8868913043748642</v>
       </c>
       <c r="E78">
-        <v>-0.1347003727177895</v>
+        <v>-0.1347003727177893</v>
       </c>
       <c r="F78">
-        <v>0.4123706747412693</v>
+        <v>0.4123706747412706</v>
       </c>
       <c r="G78">
-        <v>-0.1768989418720753</v>
+        <v>-0.1768989418720761</v>
       </c>
     </row>
     <row r="79">
@@ -2482,19 +2482,19 @@
         </is>
       </c>
       <c r="C79">
-        <v>0.8415695840433953</v>
+        <v>0.841569584043395</v>
       </c>
       <c r="D79">
-        <v>-1.356231084891103</v>
+        <v>-1.356231084891104</v>
       </c>
       <c r="E79">
-        <v>0.1890962774318939</v>
+        <v>0.1890962774318926</v>
       </c>
       <c r="F79">
-        <v>0.3545062426921285</v>
+        <v>0.3545062426921284</v>
       </c>
       <c r="G79">
-        <v>0.3039710741465713</v>
+        <v>0.3039710741465705</v>
       </c>
     </row>
     <row r="80">
@@ -2509,16 +2509,16 @@
         </is>
       </c>
       <c r="C80">
-        <v>0.303240046048814</v>
+        <v>0.3032400460488134</v>
       </c>
       <c r="D80">
-        <v>-0.6348962106593807</v>
+        <v>-0.6348962106593818</v>
       </c>
       <c r="E80">
-        <v>0.6083825022438755</v>
+        <v>0.6083825022438742</v>
       </c>
       <c r="F80">
-        <v>0.1054370472020802</v>
+        <v>0.1054370472020797</v>
       </c>
       <c r="G80">
         <v>-1.184041179670209</v>
@@ -2536,19 +2536,19 @@
         </is>
       </c>
       <c r="C81">
-        <v>-2.388280973255879</v>
+        <v>-2.388280973255878</v>
       </c>
       <c r="D81">
-        <v>1.586168942409572</v>
+        <v>1.586168942409574</v>
       </c>
       <c r="E81">
-        <v>-1.657253651638629</v>
+        <v>-1.65725365163863</v>
       </c>
       <c r="F81">
-        <v>-1.212221528745273</v>
+        <v>-1.212221528745269</v>
       </c>
       <c r="G81">
-        <v>-0.9863089460686902</v>
+        <v>-0.9863089460686889</v>
       </c>
     </row>
     <row r="82">
@@ -2563,19 +2563,19 @@
         </is>
       </c>
       <c r="C82">
-        <v>1.140664242013706</v>
+        <v>1.140664242013705</v>
       </c>
       <c r="D82">
-        <v>-0.8657071301250511</v>
+        <v>-0.8657071301250518</v>
       </c>
       <c r="E82">
-        <v>-0.1033720924827914</v>
+        <v>-0.1033720924827933</v>
       </c>
       <c r="F82">
-        <v>-0.2796912696826996</v>
+        <v>-0.2796912696826993</v>
       </c>
       <c r="G82">
-        <v>-0.1634747792428058</v>
+        <v>-0.1634747792428063</v>
       </c>
     </row>
     <row r="83">
@@ -2593,16 +2593,16 @@
         <v>1.130766915485775</v>
       </c>
       <c r="D83">
-        <v>-0.3206573621167669</v>
+        <v>-0.3206573621167687</v>
       </c>
       <c r="E83">
-        <v>1.186207021053303</v>
+        <v>1.186207021053301</v>
       </c>
       <c r="F83">
-        <v>-0.1832908282817099</v>
+        <v>-0.1832908282817106</v>
       </c>
       <c r="G83">
-        <v>0.2191746359274928</v>
+        <v>0.2191746359274922</v>
       </c>
     </row>
     <row r="84">
@@ -2617,19 +2617,19 @@
         </is>
       </c>
       <c r="C84">
-        <v>-3.014616009120254</v>
+        <v>-3.014616009120253</v>
       </c>
       <c r="D84">
-        <v>0.968567915256855</v>
+        <v>0.9685679152568536</v>
       </c>
       <c r="E84">
-        <v>2.053651425949405</v>
+        <v>2.053651425949406</v>
       </c>
       <c r="F84">
-        <v>1.143703255790425</v>
+        <v>1.143703255790424</v>
       </c>
       <c r="G84">
-        <v>-1.397599887148664</v>
+        <v>-1.397599887148663</v>
       </c>
     </row>
     <row r="85">
@@ -2644,19 +2644,19 @@
         </is>
       </c>
       <c r="C85">
-        <v>1.502679405020344</v>
+        <v>1.502679405020347</v>
       </c>
       <c r="D85">
-        <v>2.780841953579466</v>
+        <v>2.780841953579461</v>
       </c>
       <c r="E85">
-        <v>1.379169542169875</v>
+        <v>1.379169542169876</v>
       </c>
       <c r="F85">
-        <v>0.6353215647423689</v>
+        <v>0.6353215647423697</v>
       </c>
       <c r="G85">
-        <v>0.4704266568185714</v>
+        <v>0.4704266568185702</v>
       </c>
     </row>
     <row r="86">
@@ -2671,19 +2671,19 @@
         </is>
       </c>
       <c r="C86">
-        <v>0.920209287882495</v>
+        <v>0.9202092878824962</v>
       </c>
       <c r="D86">
-        <v>0.9854763922874724</v>
+        <v>0.9854763922874706</v>
       </c>
       <c r="E86">
-        <v>0.5232798065277537</v>
+        <v>0.5232798065277529</v>
       </c>
       <c r="F86">
-        <v>-0.3563193458509506</v>
+        <v>-0.3563193458509498</v>
       </c>
       <c r="G86">
-        <v>0.02845396200163374</v>
+        <v>0.02845396200163319</v>
       </c>
     </row>
     <row r="87">
@@ -2698,19 +2698,19 @@
         </is>
       </c>
       <c r="C87">
-        <v>0.001526570347461728</v>
+        <v>0.001526570347461719</v>
       </c>
       <c r="D87">
-        <v>-0.8007685699179206</v>
+        <v>-0.8007685699179214</v>
       </c>
       <c r="E87">
-        <v>0.4705612242904257</v>
+        <v>0.4705612242904248</v>
       </c>
       <c r="F87">
-        <v>0.3199092222691977</v>
+        <v>0.3199092222691978</v>
       </c>
       <c r="G87">
-        <v>0.1332702464437882</v>
+        <v>0.1332702464437879</v>
       </c>
     </row>
     <row r="88">
@@ -2725,19 +2725,19 @@
         </is>
       </c>
       <c r="C88">
-        <v>1.802307804435351</v>
+        <v>1.802307804435352</v>
       </c>
       <c r="D88">
-        <v>-0.2335621739651933</v>
+        <v>-0.2335621739651949</v>
       </c>
       <c r="E88">
-        <v>0.4333667391292966</v>
+        <v>0.4333667391292947</v>
       </c>
       <c r="F88">
-        <v>-0.4347622012344434</v>
+        <v>-0.4347622012344433</v>
       </c>
       <c r="G88">
-        <v>0.2106627874167913</v>
+        <v>0.2106627874167905</v>
       </c>
     </row>
     <row r="89">
@@ -2758,7 +2758,7 @@
         <v>-0.3599785541038832</v>
       </c>
       <c r="E89">
-        <v>0.9100053438175254</v>
+        <v>0.9100053438175242</v>
       </c>
       <c r="F89">
         <v>-0.1500748932003858</v>
@@ -2782,16 +2782,16 @@
         <v>-1.52746378579105</v>
       </c>
       <c r="D90">
-        <v>-0.7641265193608811</v>
+        <v>-0.7641265193608819</v>
       </c>
       <c r="E90">
-        <v>-0.4627550334361025</v>
+        <v>-0.4627550334361015</v>
       </c>
       <c r="F90">
-        <v>1.575358674920066</v>
+        <v>1.575358674920067</v>
       </c>
       <c r="G90">
-        <v>-0.08522072498499392</v>
+        <v>-0.08522072498499431</v>
       </c>
     </row>
     <row r="91">
@@ -2812,13 +2812,13 @@
         <v>-1.242626622142205</v>
       </c>
       <c r="E91">
-        <v>-0.09229808706865228</v>
+        <v>-0.09229808706865383</v>
       </c>
       <c r="F91">
-        <v>0.0855220783765113</v>
+        <v>0.08552207837651205</v>
       </c>
       <c r="G91">
-        <v>0.8211765860120506</v>
+        <v>0.8211765860120505</v>
       </c>
     </row>
     <row r="92">
@@ -2833,19 +2833,19 @@
         </is>
       </c>
       <c r="C92">
-        <v>-0.2423152597834958</v>
+        <v>-0.2423152597834947</v>
       </c>
       <c r="D92">
-        <v>0.6774358482342245</v>
+        <v>0.6774358482342219</v>
       </c>
       <c r="E92">
-        <v>-1.019457887439015</v>
+        <v>-1.019457887439012</v>
       </c>
       <c r="F92">
-        <v>2.266789477653696</v>
+        <v>2.266789477653699</v>
       </c>
       <c r="G92">
-        <v>0.6400981559392463</v>
+        <v>0.6400981559392454</v>
       </c>
     </row>
     <row r="93">
@@ -2860,19 +2860,19 @@
         </is>
       </c>
       <c r="C93">
-        <v>0.5597944780408818</v>
+        <v>0.5597944780408819</v>
       </c>
       <c r="D93">
-        <v>-0.1990899546698292</v>
+        <v>-0.1990899546698307</v>
       </c>
       <c r="E93">
-        <v>0.227637531870061</v>
+        <v>0.2276375318700604</v>
       </c>
       <c r="F93">
-        <v>0.3315701748443518</v>
+        <v>0.3315701748443522</v>
       </c>
       <c r="G93">
-        <v>-0.1687404523091273</v>
+        <v>-0.1687404523091279</v>
       </c>
     </row>
     <row r="94">
@@ -2887,19 +2887,19 @@
         </is>
       </c>
       <c r="C94">
-        <v>0.8545020072722849</v>
+        <v>0.8545020072722841</v>
       </c>
       <c r="D94">
         <v>-1.173766782743815</v>
       </c>
       <c r="E94">
-        <v>-0.3789721434815391</v>
+        <v>-0.378972143481541</v>
       </c>
       <c r="F94">
-        <v>-0.1876788517919661</v>
+        <v>-0.1876788517919656</v>
       </c>
       <c r="G94">
-        <v>-0.3716394995146742</v>
+        <v>-0.3716394995146747</v>
       </c>
     </row>
     <row r="95">
@@ -2917,16 +2917,16 @@
         <v>1.449434407482418</v>
       </c>
       <c r="D95">
-        <v>-1.020944505868262</v>
+        <v>-1.020944505868263</v>
       </c>
       <c r="E95">
-        <v>-0.2699743495012077</v>
+        <v>-0.2699743495012094</v>
       </c>
       <c r="F95">
-        <v>-0.02850084274002294</v>
+        <v>-0.0285008427400223</v>
       </c>
       <c r="G95">
-        <v>0.6306041574108117</v>
+        <v>0.6306041574108109</v>
       </c>
     </row>
     <row r="96">
@@ -2941,19 +2941,19 @@
         </is>
       </c>
       <c r="C96">
-        <v>0.3353652054680869</v>
+        <v>0.335365205468087</v>
       </c>
       <c r="D96">
-        <v>-0.8802850797223675</v>
+        <v>-0.8802850797223686</v>
       </c>
       <c r="E96">
-        <v>0.1609442842899922</v>
+        <v>0.1609442842899916</v>
       </c>
       <c r="F96">
-        <v>0.6771881797520906</v>
+        <v>0.6771881797520911</v>
       </c>
       <c r="G96">
-        <v>0.7587219812103562</v>
+        <v>0.7587219812103555</v>
       </c>
     </row>
     <row r="97">
@@ -2971,16 +2971,16 @@
         <v>1.030629096295535</v>
       </c>
       <c r="D97">
-        <v>0.8114651126195883</v>
+        <v>0.811465112619586</v>
       </c>
       <c r="E97">
-        <v>0.1200787009504459</v>
+        <v>0.1200787009504458</v>
       </c>
       <c r="F97">
-        <v>0.3093003490256248</v>
+        <v>0.3093003490256261</v>
       </c>
       <c r="G97">
-        <v>0.07772467161292555</v>
+        <v>0.07772467161292469</v>
       </c>
     </row>
     <row r="98">
@@ -3001,13 +3001,13 @@
         <v>-1.387368462525497</v>
       </c>
       <c r="E98">
-        <v>-0.3429417268118515</v>
+        <v>-0.3429417268118536</v>
       </c>
       <c r="F98">
-        <v>-0.1227400012266935</v>
+        <v>-0.1227400012266931</v>
       </c>
       <c r="G98">
-        <v>0.4430886173158248</v>
+        <v>0.4430886173158241</v>
       </c>
     </row>
     <row r="99">
@@ -3022,19 +3022,19 @@
         </is>
       </c>
       <c r="C99">
-        <v>0.6520034319525807</v>
+        <v>0.6520034319525815</v>
       </c>
       <c r="D99">
-        <v>-0.2114737660188336</v>
+        <v>-0.2114737660188349</v>
       </c>
       <c r="E99">
-        <v>1.433588439612692</v>
+        <v>1.433588439612691</v>
       </c>
       <c r="F99">
-        <v>-0.2482130417425434</v>
+        <v>-0.248213041742544</v>
       </c>
       <c r="G99">
-        <v>0.6825276059207285</v>
+        <v>0.6825276059207279</v>
       </c>
     </row>
     <row r="100">
@@ -3049,19 +3049,19 @@
         </is>
       </c>
       <c r="C100">
-        <v>-0.5671585486943631</v>
+        <v>-0.5671585486943636</v>
       </c>
       <c r="D100">
-        <v>-0.39097874566389</v>
+        <v>-0.3909787456638886</v>
       </c>
       <c r="E100">
-        <v>-1.100294660470957</v>
+        <v>-1.10029466047096</v>
       </c>
       <c r="F100">
-        <v>-1.399988934497475</v>
+        <v>-1.399988934497473</v>
       </c>
       <c r="G100">
-        <v>-0.441115200352722</v>
+        <v>-0.4411152003527213</v>
       </c>
     </row>
     <row r="101">
@@ -3076,19 +3076,19 @@
         </is>
       </c>
       <c r="C101">
-        <v>0.7569329978165124</v>
+        <v>0.7569329978165121</v>
       </c>
       <c r="D101">
         <v>-0.6425618958200663</v>
       </c>
       <c r="E101">
-        <v>-0.4636475277160217</v>
+        <v>-0.463647527716024</v>
       </c>
       <c r="F101">
-        <v>-0.8176350174518779</v>
+        <v>-0.8176350174518769</v>
       </c>
       <c r="G101">
-        <v>-0.3193197099667233</v>
+        <v>-0.3193197099667234</v>
       </c>
     </row>
     <row r="102">
@@ -3103,19 +3103,19 @@
         </is>
       </c>
       <c r="C102">
-        <v>0.06694021026286151</v>
+        <v>0.06694021026286093</v>
       </c>
       <c r="D102">
-        <v>-0.8361779396508563</v>
+        <v>-0.8361779396508556</v>
       </c>
       <c r="E102">
-        <v>-0.6766075256173896</v>
+        <v>-0.676607525617392</v>
       </c>
       <c r="F102">
-        <v>-0.8633166336823747</v>
+        <v>-0.8633166336823733</v>
       </c>
       <c r="G102">
-        <v>-0.4679227487037522</v>
+        <v>-0.4679227487037521</v>
       </c>
     </row>
     <row r="103">
@@ -3130,19 +3130,19 @@
         </is>
       </c>
       <c r="C103">
-        <v>-0.05612198869982429</v>
+        <v>-0.05612198869982384</v>
       </c>
       <c r="D103">
-        <v>0.771196195271567</v>
+        <v>0.771196195271566</v>
       </c>
       <c r="E103">
-        <v>-0.9789608803535327</v>
+        <v>-0.9789608803535331</v>
       </c>
       <c r="F103">
-        <v>-0.1351025896153358</v>
+        <v>-0.1351025896153332</v>
       </c>
       <c r="G103">
-        <v>-0.360279849418485</v>
+        <v>-0.3602798494184852</v>
       </c>
     </row>
     <row r="104">
@@ -3157,19 +3157,19 @@
         </is>
       </c>
       <c r="C104">
-        <v>0.6469952182244533</v>
+        <v>0.6469952182244531</v>
       </c>
       <c r="D104">
-        <v>0.2065010256500861</v>
+        <v>0.2065010256500838</v>
       </c>
       <c r="E104">
-        <v>-1.5744278112921</v>
+        <v>-1.574427811292099</v>
       </c>
       <c r="F104">
-        <v>1.599574052384217</v>
+        <v>1.599574052384219</v>
       </c>
       <c r="G104">
-        <v>-0.3724474102241001</v>
+        <v>-0.3724474102241012</v>
       </c>
     </row>
     <row r="105">
@@ -3184,19 +3184,19 @@
         </is>
       </c>
       <c r="C105">
-        <v>0.4304628812381322</v>
+        <v>0.4304628812381331</v>
       </c>
       <c r="D105">
-        <v>1.659349464430425</v>
+        <v>1.659349464430424</v>
       </c>
       <c r="E105">
-        <v>-1.932616456143718</v>
+        <v>-1.932616456143719</v>
       </c>
       <c r="F105">
-        <v>-0.467935564070368</v>
+        <v>-0.4679355640703641</v>
       </c>
       <c r="G105">
-        <v>-0.2689217570391491</v>
+        <v>-0.2689217570391493</v>
       </c>
     </row>
     <row r="106">
@@ -3211,19 +3211,19 @@
         </is>
       </c>
       <c r="C106">
-        <v>-3.204493308692672</v>
+        <v>-3.204493308692671</v>
       </c>
       <c r="D106">
-        <v>1.253902080999942</v>
+        <v>1.253902080999943</v>
       </c>
       <c r="E106">
-        <v>-0.1284050979337897</v>
+        <v>-0.1284050979337901</v>
       </c>
       <c r="F106">
-        <v>-0.5603650485336301</v>
+        <v>-0.5603650485336275</v>
       </c>
       <c r="G106">
-        <v>-0.5270661637444614</v>
+        <v>-0.52706616374446</v>
       </c>
     </row>
     <row r="107">
@@ -3238,19 +3238,19 @@
         </is>
       </c>
       <c r="C107">
-        <v>-0.626454359552665</v>
+        <v>-0.6264543595526652</v>
       </c>
       <c r="D107">
-        <v>-0.4480447009623715</v>
+        <v>-0.4480447009623713</v>
       </c>
       <c r="E107">
-        <v>-0.06402252468519098</v>
+        <v>-0.06402252468519268</v>
       </c>
       <c r="F107">
-        <v>-0.4080160770164787</v>
+        <v>-0.4080160770164778</v>
       </c>
       <c r="G107">
-        <v>-0.2389480317834214</v>
+        <v>-0.2389480317834212</v>
       </c>
     </row>
     <row r="108">
@@ -3265,19 +3265,19 @@
         </is>
       </c>
       <c r="C108">
-        <v>0.4912578025680436</v>
+        <v>0.4912578025680426</v>
       </c>
       <c r="D108">
         <v>-1.4432689531734</v>
       </c>
       <c r="E108">
-        <v>-0.3515656771910725</v>
+        <v>-0.3515656771910742</v>
       </c>
       <c r="F108">
-        <v>0.078554927849891</v>
+        <v>0.07855492784989145</v>
       </c>
       <c r="G108">
-        <v>-0.3856394568239649</v>
+        <v>-0.3856394568239654</v>
       </c>
     </row>
     <row r="109">
@@ -3292,19 +3292,19 @@
         </is>
       </c>
       <c r="C109">
-        <v>1.732548279806944</v>
+        <v>1.732548279806946</v>
       </c>
       <c r="D109">
-        <v>0.5218668524781134</v>
+        <v>0.5218668524781108</v>
       </c>
       <c r="E109">
-        <v>2.338514159371307</v>
+        <v>2.338514159371306</v>
       </c>
       <c r="F109">
-        <v>-0.505118564089412</v>
+        <v>-0.5051185640894137</v>
       </c>
       <c r="G109">
-        <v>0.5360829887339746</v>
+        <v>0.5360829887339736</v>
       </c>
     </row>
     <row r="110">
@@ -3319,19 +3319,19 @@
         </is>
       </c>
       <c r="C110">
-        <v>-3.302037306672813</v>
+        <v>-3.302037306672812</v>
       </c>
       <c r="D110">
-        <v>-0.916758855154892</v>
+        <v>-0.9167588551548898</v>
       </c>
       <c r="E110">
-        <v>-0.3191337126676228</v>
+        <v>-0.3191337126676241</v>
       </c>
       <c r="F110">
-        <v>-0.04516059254157806</v>
+        <v>-0.0451605925415759</v>
       </c>
       <c r="G110">
-        <v>1.947787925409855</v>
+        <v>1.947787925409857</v>
       </c>
     </row>
     <row r="111">
@@ -3346,19 +3346,19 @@
         </is>
       </c>
       <c r="C111">
-        <v>0.4983688492752468</v>
+        <v>0.498368849275248</v>
       </c>
       <c r="D111">
-        <v>0.6344013299109942</v>
+        <v>0.6344013299109916</v>
       </c>
       <c r="E111">
-        <v>2.58205354234222</v>
+        <v>2.582053542342219</v>
       </c>
       <c r="F111">
-        <v>-0.1140823053079331</v>
+        <v>-0.1140823053079346</v>
       </c>
       <c r="G111">
-        <v>0.06934911280024805</v>
+        <v>0.06934911280024753</v>
       </c>
     </row>
     <row r="112">
@@ -3376,16 +3376,16 @@
         <v>0.9502726699333003</v>
       </c>
       <c r="D112">
-        <v>-0.1799788143630227</v>
+        <v>-0.1799788143630252</v>
       </c>
       <c r="E112">
-        <v>2.114482418075992</v>
+        <v>2.114482418075991</v>
       </c>
       <c r="F112">
-        <v>0.2844627834576104</v>
+        <v>0.2844627834576084</v>
       </c>
       <c r="G112">
-        <v>-0.7054043090511135</v>
+        <v>-0.7054043090511144</v>
       </c>
     </row>
     <row r="113">
@@ -3403,16 +3403,16 @@
         <v>-1.754298351506857</v>
       </c>
       <c r="D113">
-        <v>0.277070399551726</v>
+        <v>0.2770703995517239</v>
       </c>
       <c r="E113">
-        <v>1.789874696272624</v>
+        <v>1.789874696272626</v>
       </c>
       <c r="F113">
-        <v>1.532879887630528</v>
+        <v>1.532879887630527</v>
       </c>
       <c r="G113">
-        <v>-0.659542994575442</v>
+        <v>-0.6595429945754423</v>
       </c>
     </row>
     <row r="114">
@@ -3427,19 +3427,19 @@
         </is>
       </c>
       <c r="C114">
-        <v>-1.162734340747173</v>
+        <v>-1.162734340747172</v>
       </c>
       <c r="D114">
-        <v>1.386810239142103</v>
+        <v>1.386810239142104</v>
       </c>
       <c r="E114">
-        <v>-1.252698540698012</v>
+        <v>-1.252698540698013</v>
       </c>
       <c r="F114">
-        <v>-0.9085610254004506</v>
+        <v>-0.9085610254004473</v>
       </c>
       <c r="G114">
-        <v>0.2165164646827429</v>
+        <v>0.2165164646827436</v>
       </c>
     </row>
     <row r="115">
@@ -3454,19 +3454,19 @@
         </is>
       </c>
       <c r="C115">
-        <v>0.3575642825256371</v>
+        <v>0.3575642825256367</v>
       </c>
       <c r="D115">
         <v>-1.305453958185328</v>
       </c>
       <c r="E115">
-        <v>-0.398475466840927</v>
+        <v>-0.398475466840929</v>
       </c>
       <c r="F115">
-        <v>-0.1657949635425457</v>
+        <v>-0.1657949635425449</v>
       </c>
       <c r="G115">
-        <v>0.4039306923847297</v>
+        <v>0.4039306923847295</v>
       </c>
     </row>
     <row r="116">
@@ -3484,16 +3484,16 @@
         <v>-1.94895403781453</v>
       </c>
       <c r="D116">
-        <v>0.2946927161712367</v>
+        <v>0.2946927161712373</v>
       </c>
       <c r="E116">
-        <v>0.1758750407404813</v>
+        <v>0.1758750407404799</v>
       </c>
       <c r="F116">
-        <v>-0.6553567410629333</v>
+        <v>-0.6553567410629321</v>
       </c>
       <c r="G116">
-        <v>-0.8902676827503235</v>
+        <v>-0.8902676827503226</v>
       </c>
     </row>
     <row r="117">
@@ -3508,19 +3508,19 @@
         </is>
       </c>
       <c r="C117">
-        <v>-4.383903770681425</v>
+        <v>-4.383903770681424</v>
       </c>
       <c r="D117">
-        <v>-0.3276034668496586</v>
+        <v>-0.3276034668496577</v>
       </c>
       <c r="E117">
-        <v>0.8110299734376254</v>
+        <v>0.811029973437626</v>
       </c>
       <c r="F117">
-        <v>1.100508186974371</v>
+        <v>1.100508186974372</v>
       </c>
       <c r="G117">
-        <v>0.165760775060163</v>
+        <v>0.165760775060164</v>
       </c>
     </row>
     <row r="118">
@@ -3535,19 +3535,19 @@
         </is>
       </c>
       <c r="C118">
-        <v>1.486453705631575</v>
+        <v>1.486453705631574</v>
       </c>
       <c r="D118">
         <v>-1.363132089494398</v>
       </c>
       <c r="E118">
-        <v>-0.8762059019894998</v>
+        <v>-0.8762059019895023</v>
       </c>
       <c r="F118">
-        <v>-0.4794078595278181</v>
+        <v>-0.479407859527817</v>
       </c>
       <c r="G118">
-        <v>0.3071132644251723</v>
+        <v>0.307113264425172</v>
       </c>
     </row>
     <row r="119">
@@ -3562,19 +3562,19 @@
         </is>
       </c>
       <c r="C119">
-        <v>-1.231100177648326</v>
+        <v>-1.231100177648327</v>
       </c>
       <c r="D119">
-        <v>-0.4277230721038735</v>
+        <v>-0.4277230721038738</v>
       </c>
       <c r="E119">
-        <v>-0.03099959270812925</v>
+        <v>-0.03099959270812958</v>
       </c>
       <c r="F119">
-        <v>0.4314928905077611</v>
+        <v>0.4314928905077619</v>
       </c>
       <c r="G119">
-        <v>-0.9158359630010829</v>
+        <v>-0.9158359630010828</v>
       </c>
     </row>
     <row r="120">
@@ -3589,16 +3589,16 @@
         </is>
       </c>
       <c r="C120">
-        <v>-0.5019117429836478</v>
+        <v>-0.5019117429836488</v>
       </c>
       <c r="D120">
-        <v>-0.8140925416654541</v>
+        <v>-0.8140925416654553</v>
       </c>
       <c r="E120">
-        <v>0.3498713001424508</v>
+        <v>0.3498713001424505</v>
       </c>
       <c r="F120">
-        <v>0.8629639908443937</v>
+        <v>0.8629639908443933</v>
       </c>
       <c r="G120">
         <v>-1.895689087842813</v>
@@ -3616,16 +3616,16 @@
         </is>
       </c>
       <c r="C121">
-        <v>0.289419643016234</v>
+        <v>0.2894196430162345</v>
       </c>
       <c r="D121">
-        <v>-0.3505514048867053</v>
+        <v>-0.3505514048867054</v>
       </c>
       <c r="E121">
-        <v>-1.13593187203705</v>
+        <v>-1.135931872037051</v>
       </c>
       <c r="F121">
-        <v>-0.03409470510548961</v>
+        <v>-0.03409470510548733</v>
       </c>
       <c r="G121">
         <v>1.177216939962532</v>
@@ -3643,19 +3643,19 @@
         </is>
       </c>
       <c r="C122">
-        <v>-0.7824835590430756</v>
+        <v>-0.7824835590430759</v>
       </c>
       <c r="D122">
         <v>-0.4780188843905893</v>
       </c>
       <c r="E122">
-        <v>0.227338741262831</v>
+        <v>0.2273387412628295</v>
       </c>
       <c r="F122">
-        <v>-0.3044131205149093</v>
+        <v>-0.3044131205149088</v>
       </c>
       <c r="G122">
-        <v>-0.6420404287530236</v>
+        <v>-0.6420404287530234</v>
       </c>
     </row>
     <row r="123">
@@ -3673,16 +3673,16 @@
         <v>-1.362467825044447</v>
       </c>
       <c r="D123">
-        <v>-0.5855160347451889</v>
+        <v>-0.5855160347451884</v>
       </c>
       <c r="E123">
-        <v>-0.2140358057931591</v>
+        <v>-0.21403580579316</v>
       </c>
       <c r="F123">
-        <v>0.1173937241275543</v>
+        <v>0.1173937241275557</v>
       </c>
       <c r="G123">
-        <v>0.1986680495078857</v>
+        <v>0.198668049507886</v>
       </c>
     </row>
     <row r="124">
@@ -3697,19 +3697,19 @@
         </is>
       </c>
       <c r="C124">
-        <v>0.1013928529986945</v>
+        <v>0.1013928529986949</v>
       </c>
       <c r="D124">
-        <v>0.9749520633633679</v>
+        <v>0.9749520633633658</v>
       </c>
       <c r="E124">
-        <v>-1.344897267807381</v>
+        <v>-1.344897267807379</v>
       </c>
       <c r="F124">
-        <v>1.022672663821111</v>
+        <v>1.022672663821114</v>
       </c>
       <c r="G124">
-        <v>-0.5744410620701325</v>
+        <v>-0.574441062070133</v>
       </c>
     </row>
     <row r="125">
@@ -3724,19 +3724,19 @@
         </is>
       </c>
       <c r="C125">
-        <v>-2.072258892325523</v>
+        <v>-2.072258892325522</v>
       </c>
       <c r="D125">
-        <v>1.255269012552742</v>
+        <v>1.255269012552743</v>
       </c>
       <c r="E125">
-        <v>1.278067113101706</v>
+        <v>1.278067113101704</v>
       </c>
       <c r="F125">
-        <v>-1.096543207124924</v>
+        <v>-1.096543207124923</v>
       </c>
       <c r="G125">
-        <v>-0.3601713592445966</v>
+        <v>-0.3601713592445956</v>
       </c>
     </row>
     <row r="126">
@@ -3751,19 +3751,19 @@
         </is>
       </c>
       <c r="C126">
-        <v>-1.429674238719123</v>
+        <v>-1.429674238719122</v>
       </c>
       <c r="D126">
-        <v>0.6038959920979002</v>
+        <v>0.6038959920979008</v>
       </c>
       <c r="E126">
-        <v>-0.7464267374098444</v>
+        <v>-0.7464267374098457</v>
       </c>
       <c r="F126">
-        <v>-0.487376639946739</v>
+        <v>-0.487376639946736</v>
       </c>
       <c r="G126">
-        <v>0.9821172394484982</v>
+        <v>0.9821172394484989</v>
       </c>
     </row>
   </sheetData>
